--- a/datasetsWC26/jugadores.xlsx
+++ b/datasetsWC26/jugadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/be072d6543165b68/isabel millington/ICAI/segundo/adquisición y visualización de datos/proyecto/datasetsWC26/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_46C1C688D76FE40E62355476585DCE3A874BC92B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_46C135E8537C2E0E62355476585DCE3A874BC92B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
